--- a/data/trans_orig/IQ21A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ21A-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el número de veces que han estado hospitalizados a lo largo de estos últimos 12 meses</t>
+          <t>Menores según el número de veces que han estado hospitalizados a lo largo de estos últimos 12 meses (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,12 +716,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,26</t>
+          <t>1,0; 1,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,4</t>
+          <t>1,04; 1,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -741,12 +741,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,25</t>
+          <t>1,13; 2,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,96</t>
+          <t>1,11; 4,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,17 +756,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,14</t>
+          <t>1,0; 1,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 1,68</t>
+          <t>1,13; 1,69</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,54</t>
+          <t>1,05; 2,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,32</t>
+          <t>1,0; 1,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,83</t>
+          <t>1,11; 1,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,12</t>
+          <t>1,14; 3,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,49</t>
+          <t>1,0; 1,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,72</t>
+          <t>1,1; 2,7</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,64</t>
+          <t>1,07; 1,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,71</t>
+          <t>1,0; 1,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 24,33</t>
+          <t>1,0; 30,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1036,17 +1036,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,47</t>
+          <t>1,0; 1,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,61</t>
+          <t>1,0; 1,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 17,98</t>
+          <t>1,0; 18,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,59</t>
+          <t>1,0; 1,64</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1276,17 +1276,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,23</t>
+          <t>1,0; 1,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,26</t>
+          <t>1,05; 1,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,37</t>
+          <t>1,07; 1,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1296,17 +1296,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,76</t>
+          <t>1,06; 1,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,51</t>
+          <t>1,08; 1,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 10,71</t>
+          <t>1,09; 11,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,41</t>
+          <t>1,05; 1,38</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,23</t>
+          <t>1,16; 5,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">

--- a/data/trans_orig/IQ21A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ21A-Edad-trans_orig.xlsx
@@ -716,12 +716,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,27</t>
+          <t>1,0; 1,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,38</t>
+          <t>1,04; 1,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -741,12 +741,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,27</t>
+          <t>1,13; 2,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,15</t>
+          <t>1,11; 4,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,17 +756,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,11</t>
+          <t>1,0; 1,13</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 1,69</t>
+          <t>1,13; 1,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,77</t>
+          <t>1,05; 2,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,34</t>
+          <t>1,0; 1,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 1,88</t>
+          <t>1,1; 1,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,02</t>
+          <t>1,14; 3,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,57</t>
+          <t>1,0; 1,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -896,17 +896,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,7</t>
+          <t>1,1; 2,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,31</t>
+          <t>1,03; 1,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,59</t>
+          <t>1,07; 1,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,72</t>
+          <t>1,0; 1,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,41</t>
+          <t>1,0; 1,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 30,93</t>
+          <t>1,0; 30,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1036,17 +1036,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,39</t>
+          <t>1,0; 1,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,6</t>
+          <t>1,0; 1,61</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 18,36</t>
+          <t>1,06; 21,76</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,64</t>
+          <t>1,0; 1,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,2</t>
+          <t>1,0; 1,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,36</t>
+          <t>1,07; 1,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1296,17 +1296,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,62</t>
+          <t>1,06; 1,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,54</t>
+          <t>1,1; 1,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 11,27</t>
+          <t>1,12; 11,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,38</t>
+          <t>1,04; 1,4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,35</t>
+          <t>1,09; 1,34</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,86</t>
+          <t>1,15; 6,18</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
